--- a/output/yearly_surface_area_iteration_82_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_82_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497609695363</v>
+        <v>10.84497636829007</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907112214645</v>
+        <v>37.78907206761205</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.726935269499145</v>
+        <v>7.176575718044184</v>
       </c>
       <c r="C2" t="n">
-        <v>6.982189672603315</v>
+        <v>6.732825755724625</v>
       </c>
       <c r="D2" t="n">
-        <v>25.53329429205104</v>
+        <v>30.62365613857076</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.75967710110456</v>
+        <v>24.42097414313941</v>
       </c>
       <c r="C3" t="n">
-        <v>38.14089830998858</v>
+        <v>30.28200793749286</v>
       </c>
       <c r="D3" t="n">
-        <v>70.90181920070465</v>
+        <v>81.23471378790232</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.6274853183965</v>
+        <v>41.32568786256524</v>
       </c>
       <c r="C4" t="n">
-        <v>89.93888893375454</v>
+        <v>59.89544568839366</v>
       </c>
       <c r="D4" t="n">
-        <v>93.79323042062752</v>
+        <v>92.37656848339938</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.97095814616266</v>
+        <v>52.98983233672161</v>
       </c>
       <c r="C5" t="n">
-        <v>142.9670094309418</v>
+        <v>107.5504610002381</v>
       </c>
       <c r="D5" t="n">
-        <v>75.49639845657973</v>
+        <v>64.59899893944014</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.07556318216056</v>
+        <v>51.11960296013142</v>
       </c>
       <c r="C6" t="n">
-        <v>130.1336034410275</v>
+        <v>133.67574915795</v>
       </c>
       <c r="D6" t="n">
-        <v>52.93092747446678</v>
+        <v>46.32965591111124</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.56591295046944</v>
+        <v>35.75230614555609</v>
       </c>
       <c r="C7" t="n">
-        <v>93.72254458592174</v>
+        <v>115.7009304408951</v>
       </c>
       <c r="D7" t="n">
-        <v>40.72289477215769</v>
+        <v>38.92629647338602</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>18.10833640483241</v>
       </c>
       <c r="C8" t="n">
-        <v>55.32639187282899</v>
+        <v>78.69198723390308</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>32.9484347022272</v>
+        <v>44.26405874137593</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.679564811812275</v>
+        <v>7.664533843567649</v>
       </c>
       <c r="C21" t="n">
-        <v>94.07466894470036</v>
+        <v>93.8905395837037</v>
       </c>
       <c r="D21" t="n">
-        <v>8.639510413288809</v>
+        <v>7.664533843567649</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.912886496229292</v>
+        <v>8.409650834578178</v>
       </c>
       <c r="C2" t="n">
-        <v>7.893251542144355</v>
+        <v>7.49171673110741</v>
       </c>
       <c r="D2" t="n">
-        <v>29.65663464988765</v>
+        <v>29.39058102203676</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.6846633649543</v>
+        <v>24.24916829489622</v>
       </c>
       <c r="C3" t="n">
-        <v>32.35840433197487</v>
+        <v>28.01907947920397</v>
       </c>
       <c r="D3" t="n">
-        <v>74.53428570641783</v>
+        <v>86.32998437294327</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.08243541609028</v>
+        <v>43.11246868429443</v>
       </c>
       <c r="C4" t="n">
-        <v>92.40209392370978</v>
+        <v>67.50202690089795</v>
       </c>
       <c r="D4" t="n">
-        <v>103.9395929440183</v>
+        <v>106.9260694603371</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.86144437164352</v>
+        <v>56.74501730546565</v>
       </c>
       <c r="C5" t="n">
-        <v>152.1463504656495</v>
+        <v>107.7222668484813</v>
       </c>
       <c r="D5" t="n">
-        <v>88.57818661566847</v>
+        <v>79.98789420350889</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.42023874180921</v>
+        <v>60.25672884355649</v>
       </c>
       <c r="C6" t="n">
-        <v>174.9336964289222</v>
+        <v>151.225471119066</v>
       </c>
       <c r="D6" t="n">
-        <v>63.07434475474484</v>
+        <v>53.81646390369741</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.52516257297658</v>
+        <v>47.4301950875719</v>
       </c>
       <c r="C7" t="n">
-        <v>135.8228313871377</v>
+        <v>150.3752776071882</v>
       </c>
       <c r="D7" t="n">
-        <v>45.87314322863646</v>
+        <v>42.93869934064274</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.69662426385451</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="C8" t="n">
-        <v>86.95339416514</v>
+        <v>113.4065860560703</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.42812411450962</v>
+        <v>12.53593643552752</v>
       </c>
       <c r="C9" t="n">
-        <v>48.92343334573128</v>
+        <v>68.00468172547228</v>
       </c>
       <c r="D9" t="n">
         <v>35.49999698556465</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>34.44952694202058</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.62994753542373</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.854209970984857</v>
+        <v>7.838780255698454</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1047296228031</v>
+        <v>101.9041433240799</v>
       </c>
       <c r="D21" t="n">
-        <v>9.817762463731071</v>
+        <v>8.818627787660761</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.17795837637593</v>
+        <v>9.711448290409448</v>
       </c>
       <c r="C2" t="n">
-        <v>8.994772466309277</v>
+        <v>6.634650985299944</v>
       </c>
       <c r="D2" t="n">
-        <v>41.12639307860314</v>
+        <v>30.93977889933823</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.42097414313941</v>
+        <v>25.46162670964103</v>
       </c>
       <c r="C3" t="n">
-        <v>31.28339059582461</v>
+        <v>28.24488145118073</v>
       </c>
       <c r="D3" t="n">
-        <v>78.61344741756335</v>
+        <v>88.0774952865026</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.8144182928309</v>
+        <v>43.38048580755381</v>
       </c>
       <c r="C4" t="n">
-        <v>86.09731016703677</v>
+        <v>67.70623042338129</v>
       </c>
       <c r="D4" t="n">
-        <v>113.7158365829081</v>
+        <v>119.5611624139936</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.32210502911353</v>
+        <v>60.03387211469246</v>
       </c>
       <c r="C5" t="n">
-        <v>159.5094582475005</v>
+        <v>113.5636656887498</v>
       </c>
       <c r="D5" t="n">
-        <v>99.99100367753766</v>
+        <v>95.64677008624551</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.47056991663305</v>
+        <v>66.53598715991909</v>
       </c>
       <c r="C6" t="n">
-        <v>201.0570210912256</v>
+        <v>160.1210870672463</v>
       </c>
       <c r="D6" t="n">
-        <v>72.65423885278521</v>
+        <v>62.95358978712248</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.46633982617978</v>
+        <v>57.13182590093888</v>
       </c>
       <c r="C7" t="n">
-        <v>183.1931398647505</v>
+        <v>178.0428914082718</v>
       </c>
       <c r="D7" t="n">
-        <v>51.98157744446011</v>
+        <v>47.54996830749001</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.0414797499524</v>
+        <v>36.80081269369168</v>
       </c>
       <c r="C8" t="n">
-        <v>126.0073178400781</v>
+        <v>148.9556704268473</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>39.72151211382594</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.97656122828509</v>
+        <v>18.41562343626167</v>
       </c>
       <c r="C9" t="n">
-        <v>72.55311883924776</v>
+        <v>98.73436661610168</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>56.94136684631501</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>35.36157055926586</v>
+        <v>38.56010457970196</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>33.30088212805181</v>
@@ -1573,7 +1573,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -1590,7 +1590,7 @@
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.011751814082565</v>
+        <v>7.997300549697052</v>
       </c>
       <c r="C21" t="n">
-        <v>109.1601184668749</v>
+        <v>108.9632199896223</v>
       </c>
       <c r="D21" t="n">
-        <v>11.01615874436353</v>
+        <v>9.996625687121314</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.675303551801563</v>
+        <v>8.95059381961817</v>
       </c>
       <c r="C2" t="n">
-        <v>6.259623362277663</v>
+        <v>4.564145077043421</v>
       </c>
       <c r="D2" t="n">
-        <v>33.65529304928491</v>
+        <v>25.59710789282709</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.54569715930776</v>
+        <v>30.05129722699487</v>
       </c>
       <c r="C3" t="n">
-        <v>48.6946861306418</v>
+        <v>41.82736093943536</v>
       </c>
       <c r="D3" t="n">
-        <v>85.12734343524093</v>
+        <v>94.44903788706439</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.49915410658066</v>
+        <v>28.84374755077129</v>
       </c>
       <c r="C4" t="n">
-        <v>125.9042343311322</v>
+        <v>93.07851809193585</v>
       </c>
       <c r="D4" t="n">
-        <v>110.1678003797601</v>
+        <v>112.426801847232</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.19565519724816</v>
+        <v>37.47821860962199</v>
       </c>
       <c r="C5" t="n">
-        <v>120.1413753072034</v>
+        <v>95.67131377885168</v>
       </c>
       <c r="D5" t="n">
-        <v>70.26859193146547</v>
+        <v>63.32272692391928</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.71201343195298</v>
+        <v>35.46170882509904</v>
       </c>
       <c r="C6" t="n">
-        <v>120.6342126547354</v>
+        <v>117.2530735613093</v>
       </c>
       <c r="D6" t="n">
-        <v>34.21390749300134</v>
+        <v>31.31578827006476</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.8823545064064</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="C7" t="n">
-        <v>88.57229612944299</v>
+        <v>104.7416808183879</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>12.76762889372977</v>
       </c>
       <c r="C8" t="n">
-        <v>53.40707511102648</v>
+        <v>72.76713983877357</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>43.4874963073167</v>
       </c>
       <c r="D9" t="n">
         <v>27.17968519207294</v>
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.75891633757857</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
         <v>27.12078032981814</v>
@@ -1870,7 +1870,7 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1887,7 +1887,7 @@
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1971,7 +1971,7 @@
         <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.80467326458389</v>
+        <v>5.353470231257857</v>
       </c>
       <c r="C2" t="n">
-        <v>2.882411259668635</v>
+        <v>2.944261365036184</v>
       </c>
       <c r="D2" t="n">
-        <v>23.41370099858218</v>
+        <v>17.58899186928585</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.83883881225006</v>
+        <v>31.21466825652734</v>
       </c>
       <c r="C3" t="n">
-        <v>37.2916865458151</v>
+        <v>30.18874190558942</v>
       </c>
       <c r="D3" t="n">
-        <v>92.34809779997622</v>
+        <v>94.47358157967057</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.04941584704438</v>
+        <v>41.30016242225481</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2187945071187</v>
+        <v>101.9358458796506</v>
       </c>
       <c r="D4" t="n">
-        <v>123.874961826454</v>
+        <v>129.2480670117968</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.49080140332795</v>
+        <v>41.45429681182157</v>
       </c>
       <c r="C5" t="n">
-        <v>172.5912464065893</v>
+        <v>131.8487166803467</v>
       </c>
       <c r="D5" t="n">
-        <v>87.8173321448772</v>
+        <v>81.68140899333464</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.79001346894498</v>
+        <v>41.94222542083224</v>
       </c>
       <c r="C6" t="n">
-        <v>152.4732724511637</v>
+        <v>136.5738683808866</v>
       </c>
       <c r="D6" t="n">
-        <v>41.78121879733577</v>
+        <v>38.80259626265094</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>22.69702517448201</v>
       </c>
       <c r="C7" t="n">
-        <v>120.3720860177014</v>
+        <v>132.3494080095125</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>72.01610284502478</v>
+        <v>94.54721265748907</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>38.38437174064178</v>
+        <v>48.7015583645715</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2184,7 +2184,7 @@
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2268,7 +2268,7 @@
         <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.204825417289089</v>
+        <v>6.403940274801944</v>
       </c>
       <c r="C2" t="n">
-        <v>4.591634012762332</v>
+        <v>5.972953032637593</v>
       </c>
       <c r="D2" t="n">
-        <v>23.11034095796992</v>
+        <v>27.53213261789755</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.81090790817464</v>
+        <v>24.68113728476482</v>
       </c>
       <c r="C3" t="n">
-        <v>23.66011967234813</v>
+        <v>20.20436775339936</v>
       </c>
       <c r="D3" t="n">
-        <v>89.50102945766048</v>
+        <v>87.23319226085033</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.69879304790803</v>
+        <v>50.15749020996954</v>
       </c>
       <c r="C4" t="n">
-        <v>110.040173178208</v>
+        <v>89.31351564614933</v>
       </c>
       <c r="D4" t="n">
-        <v>139.0753615313074</v>
+        <v>144.3080767949429</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.64559874542947</v>
+        <v>50.60909415392309</v>
       </c>
       <c r="C5" t="n">
-        <v>203.8599107868502</v>
+        <v>158.6749726988907</v>
       </c>
       <c r="D5" t="n">
-        <v>108.2376843932109</v>
+        <v>104.8261111209532</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.39757642915352</v>
+        <v>48.30198704894308</v>
       </c>
       <c r="C6" t="n">
-        <v>207.4167827193364</v>
+        <v>171.7538156148668</v>
       </c>
       <c r="D6" t="n">
-        <v>55.94980166502573</v>
+        <v>51.96488773348793</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.90716024091983</v>
+        <v>33.53650157707104</v>
       </c>
       <c r="C7" t="n">
-        <v>166.365002466256</v>
+        <v>162.113053159163</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>15.52143120414207</v>
       </c>
       <c r="C8" t="n">
-        <v>110.1520924164921</v>
+        <v>131.5149224609027</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>59.46249495082079</v>
+        <v>78.21093085882212</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>37.43894870145212</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2495,7 +2495,7 @@
         <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2579,7 +2579,7 @@
         <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.553525778745954</v>
+        <v>3.845505757534756</v>
       </c>
       <c r="C2" t="n">
-        <v>2.180461651132166</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="D2" t="n">
-        <v>16.1301147807751</v>
+        <v>19.19513111343364</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.80952524984289</v>
+        <v>25.46653544816226</v>
       </c>
       <c r="C3" t="n">
-        <v>22.7470943073986</v>
+        <v>22.78636421556847</v>
       </c>
       <c r="D3" t="n">
-        <v>90.20297906619695</v>
+        <v>90.52204707007715</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.75733805726435</v>
+        <v>54.94351026817274</v>
       </c>
       <c r="C4" t="n">
-        <v>103.9906438246391</v>
+        <v>84.37434294608363</v>
       </c>
       <c r="D4" t="n">
-        <v>150.1406399058732</v>
+        <v>154.4927274787993</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.75006491270713</v>
+        <v>52.44987109938586</v>
       </c>
       <c r="C5" t="n">
-        <v>237.1657016534233</v>
+        <v>185.4766850248287</v>
       </c>
       <c r="D5" t="n">
-        <v>114.2263453891164</v>
+        <v>111.0111216577081</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.93843729873549</v>
+        <v>40.01014593887452</v>
       </c>
       <c r="C6" t="n">
-        <v>239.1350875481424</v>
+        <v>205.927471451994</v>
       </c>
       <c r="D6" t="n">
-        <v>54.58124536530568</v>
+        <v>50.91834468076083</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.384125394267761</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="C7" t="n">
-        <v>161.8136201093678</v>
+        <v>170.2576321135946</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>34.2551408965797</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>76.18853058807372</v>
+        <v>97.55136063248432</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>28.51093507903161</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2792,7 +2792,7 @@
         <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2876,7 +2876,7 @@
         <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.995312245657018</v>
+        <v>4.774239085752239</v>
       </c>
       <c r="C2" t="n">
-        <v>6.202681995431348</v>
+        <v>3.047344873982099</v>
       </c>
       <c r="D2" t="n">
-        <v>14.21767025290231</v>
+        <v>15.51946770873358</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.60487975900305</v>
+        <v>19.54168805303276</v>
       </c>
       <c r="C3" t="n">
-        <v>15.62451471308799</v>
+        <v>16.8222469122691</v>
       </c>
       <c r="D3" t="n">
-        <v>83.06076451780139</v>
+        <v>86.0452775387117</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.45630136495907</v>
+        <v>52.41649167744146</v>
       </c>
       <c r="C4" t="n">
-        <v>82.15362963907734</v>
+        <v>71.59886007071988</v>
       </c>
       <c r="D4" t="n">
-        <v>158.5257470478452</v>
+        <v>162.2141731727005</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.81927027808992</v>
+        <v>64.94261063592651</v>
       </c>
       <c r="C5" t="n">
-        <v>218.4388641949154</v>
+        <v>173.131207643925</v>
       </c>
       <c r="D5" t="n">
-        <v>135.8738822677586</v>
+        <v>134.4258044039945</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.25544399621598</v>
+        <v>51.60262283062086</v>
       </c>
       <c r="C6" t="n">
-        <v>299.7540812945659</v>
+        <v>246.6218955407285</v>
       </c>
       <c r="D6" t="n">
-        <v>72.2114706381699</v>
+        <v>67.86429180376503</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>22.27781890476862</v>
       </c>
       <c r="C7" t="n">
-        <v>237.4504084876548</v>
+        <v>226.850478524902</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>130.263194137988</v>
+        <v>148.7053247622644</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>52.14062057254808</v>
+        <v>63.89999457401638</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.183406894244906</v>
+        <v>3.334015203622168</v>
       </c>
       <c r="C2" t="n">
-        <v>4.793874039837175</v>
+        <v>1.926188995732242</v>
       </c>
       <c r="D2" t="n">
-        <v>10.50175519232813</v>
+        <v>10.96710360414112</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.50884841043611</v>
+        <v>18.33413837680919</v>
       </c>
       <c r="C3" t="n">
-        <v>19.51714436042659</v>
+        <v>14.72621556370216</v>
       </c>
       <c r="D3" t="n">
-        <v>77.33226666352125</v>
+        <v>80.34623211555896</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.28739970209961</v>
+        <v>47.80914970141117</v>
       </c>
       <c r="C4" t="n">
-        <v>66.45548384817084</v>
+        <v>60.92922602096554</v>
       </c>
       <c r="D4" t="n">
-        <v>162.3928512548734</v>
+        <v>168.6593468510808</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.43348448804993</v>
+        <v>71.07853378746908</v>
       </c>
       <c r="C5" t="n">
-        <v>201.380997833627</v>
+        <v>161.9147401229052</v>
       </c>
       <c r="D5" t="n">
-        <v>152.1954378508618</v>
+        <v>150.354660905399</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.74854338565514</v>
+        <v>61.54478183152831</v>
       </c>
       <c r="C6" t="n">
-        <v>329.3390483620436</v>
+        <v>270.8936440328225</v>
       </c>
       <c r="D6" t="n">
-        <v>84.32721905627979</v>
+        <v>82.19388129495147</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>20.06201433628357</v>
       </c>
       <c r="C7" t="n">
-        <v>298.2952042060551</v>
+        <v>273.0230548033337</v>
       </c>
       <c r="D7" t="n">
-        <v>44.73529763941441</v>
+        <v>43.95677170994669</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>174.7412738788898</v>
+        <v>191.7647790705294</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>58.242182554442</v>
+        <v>72.33124385808797</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.778746913645973</v>
+        <v>4.942117943178443</v>
       </c>
       <c r="C2" t="n">
-        <v>6.742643232767094</v>
+        <v>2.741039590257095</v>
       </c>
       <c r="D2" t="n">
-        <v>21.06437874231957</v>
+        <v>14.5131763118806</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.62251015995049</v>
+        <v>14.92747384307275</v>
       </c>
       <c r="C3" t="n">
-        <v>18.92318699935727</v>
+        <v>11.30482481440202</v>
       </c>
       <c r="D3" t="n">
-        <v>70.1458734684346</v>
+        <v>72.13882130805563</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.3827680981318</v>
+        <v>41.90001026954963</v>
       </c>
       <c r="C4" t="n">
-        <v>58.58088551240717</v>
+        <v>50.0936766091935</v>
       </c>
       <c r="D4" t="n">
-        <v>161.0910537990421</v>
+        <v>169.3230082991516</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.96086293167971</v>
+        <v>71.15216486528759</v>
       </c>
       <c r="C5" t="n">
-        <v>168.222469122691</v>
+        <v>140.4880964777186</v>
       </c>
       <c r="D5" t="n">
-        <v>169.0814983639069</v>
+        <v>169.1551294417254</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.34102027740147</v>
+        <v>74.3045567436241</v>
       </c>
       <c r="C6" t="n">
-        <v>326.9642006654705</v>
+        <v>266.5464651984176</v>
       </c>
       <c r="D6" t="n">
-        <v>103.8492721552276</v>
+        <v>101.6354310821511</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.33876937788993</v>
+        <v>37.54890444432775</v>
       </c>
       <c r="C7" t="n">
-        <v>367.6438985386413</v>
+        <v>321.2916624303323</v>
       </c>
       <c r="D7" t="n">
-        <v>53.71828913327272</v>
+        <v>52.70021676396878</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>258.9408657336174</v>
+        <v>260.1091455016712</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>113.2671778820672</v>
+        <v>132.0156137900686</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>49.82369599052563</v>
       </c>
       <c r="D10" t="n">
         <v>26.33538216642069</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
         <v>24.6997904911455</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.946044933995431</v>
+        <v>7.718500450788423</v>
       </c>
       <c r="C2" t="n">
-        <v>3.734568266954867</v>
+        <v>9.101782966072179</v>
       </c>
       <c r="D2" t="n">
-        <v>21.97249536874786</v>
+        <v>14.03015644139117</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.73318560862312</v>
+        <v>3.537236978401258</v>
       </c>
       <c r="C2" t="n">
-        <v>3.93680829402971</v>
+        <v>1.578650308428871</v>
       </c>
       <c r="D2" t="n">
-        <v>15.67262035059608</v>
+        <v>10.6814150222053</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.95201753567892</v>
+        <v>20.10619298297468</v>
       </c>
       <c r="C3" t="n">
-        <v>23.81229056650639</v>
+        <v>12.7283589855599</v>
       </c>
       <c r="D3" t="n">
-        <v>77.40098900281853</v>
+        <v>78.26983572107696</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.97506506342888</v>
+        <v>55.28810371236337</v>
       </c>
       <c r="C4" t="n">
-        <v>89.03273580273473</v>
+        <v>73.62813257539804</v>
       </c>
       <c r="D4" t="n">
-        <v>164.9198698456047</v>
+        <v>172.2711966550048</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.1226460142354</v>
+        <v>43.83503499462009</v>
       </c>
       <c r="C5" t="n">
-        <v>266.7899386290708</v>
+        <v>219.1260875878881</v>
       </c>
       <c r="D5" t="n">
-        <v>153.373535095958</v>
+        <v>152.1463504656495</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.04532462531138</v>
+        <v>23.30570875111504</v>
       </c>
       <c r="C6" t="n">
-        <v>299.8345846063141</v>
+        <v>263.8496042548516</v>
       </c>
       <c r="D6" t="n">
-        <v>80.62406671586082</v>
+        <v>79.98004022187492</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>6.647413705455153</v>
       </c>
       <c r="C7" t="n">
-        <v>182.0552942755285</v>
+        <v>182.8937068149553</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>32.39865598784899</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>83.44855486097887</v>
+        <v>97.30101496790137</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>24.45042657426681</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
         <v>20.07968579496001</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>19.3600647277471</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.890887136108362</v>
+        <v>7.58105577219387</v>
       </c>
       <c r="C2" t="n">
-        <v>5.90030370252333</v>
+        <v>4.968625131193107</v>
       </c>
       <c r="D2" t="n">
-        <v>19.45725775046753</v>
+        <v>14.5279025274443</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.5096091739621</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="C3" t="n">
-        <v>9.410051745205678</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D3" t="n">
-        <v>21.5935407549086</v>
+        <v>14.92256510455152</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3967416863245</v>
+        <v>13.39670792053571</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13588294605178</v>
+        <v>70.13570617221635</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576087257214647</v>
+        <v>1.576083284768907</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.077599126364503</v>
+        <v>6.807438581247383</v>
       </c>
       <c r="C2" t="n">
-        <v>6.338163178617408</v>
+        <v>6.210535977065322</v>
       </c>
       <c r="D2" t="n">
-        <v>19.2530542279842</v>
+        <v>18.12600786350886</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.44213062427633</v>
+        <v>22.30530784048753</v>
       </c>
       <c r="C3" t="n">
-        <v>17.91689560250429</v>
+        <v>20.70505908256523</v>
       </c>
       <c r="D3" t="n">
-        <v>32.71674224402496</v>
+        <v>23.51776625523235</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.30326222962103</v>
+        <v>18.95263943048468</v>
       </c>
       <c r="C4" t="n">
-        <v>14.90685714128357</v>
+        <v>35.49312475163494</v>
       </c>
       <c r="D4" t="n">
-        <v>26.39330528097125</v>
+        <v>22.89631995844411</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4388622209788</v>
+        <v>15.43738851842041</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13259975914491</v>
+        <v>86.12437805013492</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250286783363959</v>
+        <v>3.249976530193771</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.828636120113313</v>
+        <v>6.68864710903352</v>
       </c>
       <c r="C2" t="n">
-        <v>7.658613840829368</v>
+        <v>8.609927366244527</v>
       </c>
       <c r="D2" t="n">
-        <v>19.86861003854695</v>
+        <v>15.30937370002476</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.96107424919539</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="C3" t="n">
-        <v>22.00587479069226</v>
+        <v>22.75200304591983</v>
       </c>
       <c r="D3" t="n">
-        <v>40.52654523130833</v>
+        <v>32.55966261134547</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.46162670964103</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="C4" t="n">
-        <v>32.53217367562655</v>
+        <v>44.61846966260904</v>
       </c>
       <c r="D4" t="n">
-        <v>36.84597308808704</v>
+        <v>29.53293443915255</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.19192382841364</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="C5" t="n">
-        <v>18.01507037292897</v>
+        <v>39.71169463678348</v>
       </c>
       <c r="D5" t="n">
-        <v>32.10314992887071</v>
+        <v>30.87596529856219</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5336,7 +5336,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73267859256752</v>
+        <v>16.72700198391217</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0693394146619</v>
+        <v>102.0347121018642</v>
       </c>
       <c r="D21" t="n">
-        <v>5.019803577770255</v>
+        <v>4.181750495978043</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.819219553698344</v>
+        <v>6.127087422204344</v>
       </c>
       <c r="C2" t="n">
-        <v>12.18447075740716</v>
+        <v>8.151451188361266</v>
       </c>
       <c r="D2" t="n">
-        <v>21.07223272395354</v>
+        <v>26.75557018383832</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.06554041647306</v>
+        <v>22.89926520155685</v>
       </c>
       <c r="C3" t="n">
-        <v>26.44828315240908</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D3" t="n">
-        <v>46.61338099763856</v>
+        <v>36.95298358784994</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.63052837250048</v>
+        <v>38.81143199198916</v>
       </c>
       <c r="C4" t="n">
-        <v>44.80991046493716</v>
+        <v>51.49757582626644</v>
       </c>
       <c r="D4" t="n">
-        <v>48.21755674637784</v>
+        <v>38.68380479043707</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.54369260617026</v>
+        <v>32.64311116620645</v>
       </c>
       <c r="C5" t="n">
-        <v>41.15977250054753</v>
+        <v>62.75822199397737</v>
       </c>
       <c r="D5" t="n">
-        <v>37.50276230222816</v>
+        <v>34.11573272257667</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.62643715076748</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="C6" t="n">
-        <v>20.81010608691964</v>
+        <v>38.40007970390975</v>
       </c>
       <c r="D6" t="n">
-        <v>38.80259626265094</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>20.90042687571034</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.72499713628642</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0599138985599</v>
+        <v>18.04747852279032</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8194382906051</v>
+        <v>117.7383122677273</v>
       </c>
       <c r="D21" t="n">
-        <v>6.87996719945139</v>
+        <v>6.01582617426344</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.35918079103409</v>
+        <v>6.721044783273664</v>
       </c>
       <c r="C2" t="n">
-        <v>12.33467815615692</v>
+        <v>5.608724634362028</v>
       </c>
       <c r="D2" t="n">
-        <v>28.67586869334508</v>
+        <v>34.08824378685775</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.12444527872787</v>
+        <v>19.57114048416017</v>
       </c>
       <c r="C3" t="n">
-        <v>36.09395434663399</v>
+        <v>28.55904071653972</v>
       </c>
       <c r="D3" t="n">
-        <v>49.16592502868026</v>
+        <v>46.15686831516379</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.70862622048373</v>
+        <v>30.12001956629214</v>
       </c>
       <c r="C4" t="n">
-        <v>47.18377641380595</v>
+        <v>52.21228815495812</v>
       </c>
       <c r="D4" t="n">
-        <v>52.36544079682062</v>
+        <v>41.82343394861837</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.77025534167302</v>
+        <v>27.68528525976006</v>
       </c>
       <c r="C5" t="n">
-        <v>47.51658888554563</v>
+        <v>59.51845456996289</v>
       </c>
       <c r="D5" t="n">
-        <v>36.88916998707391</v>
+        <v>32.15223731408305</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.91449013873929</v>
+        <v>15.77864910265474</v>
       </c>
       <c r="C6" t="n">
-        <v>29.86672865859647</v>
+        <v>47.05418571684538</v>
       </c>
       <c r="D6" t="n">
-        <v>32.48308629041422</v>
+        <v>31.51704654943536</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>16.40893112878119</v>
+        <v>24.73316991308989</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.63281066307846</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.059018623166744</v>
+        <v>7.05062000811281</v>
       </c>
       <c r="C21" t="n">
-        <v>66.17829959218822</v>
+        <v>66.98089007707169</v>
       </c>
       <c r="D21" t="n">
-        <v>5.294263967375058</v>
+        <v>4.406637505070506</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.983171420307562</v>
+        <v>6.806456833543137</v>
       </c>
       <c r="C2" t="n">
-        <v>7.522150909939061</v>
+        <v>5.767767762450011</v>
       </c>
       <c r="D2" t="n">
-        <v>23.46867887002</v>
+        <v>28.47264691856599</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.25760311360694</v>
+        <v>21.98133109808609</v>
       </c>
       <c r="C3" t="n">
-        <v>43.90375733391736</v>
+        <v>24.32770811123596</v>
       </c>
       <c r="D3" t="n">
-        <v>61.37395773098935</v>
+        <v>63.63688618927824</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.76190263842031</v>
+        <v>35.36549755008285</v>
       </c>
       <c r="C4" t="n">
-        <v>74.41942122502097</v>
+        <v>63.73702445511142</v>
       </c>
       <c r="D4" t="n">
-        <v>65.47275439621978</v>
+        <v>56.30912132478006</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.90050899116836</v>
+        <v>37.69911184307752</v>
       </c>
       <c r="C5" t="n">
-        <v>71.8148445656542</v>
+        <v>82.22137023067039</v>
       </c>
       <c r="D5" t="n">
-        <v>48.62105505282329</v>
+        <v>40.12893741108838</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.85664913964674</v>
+        <v>28.2566624236317</v>
       </c>
       <c r="C6" t="n">
-        <v>56.714583126634</v>
+        <v>75.10958986110649</v>
       </c>
       <c r="D6" t="n">
-        <v>37.39378830705677</v>
+        <v>35.13969557810609</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.4801567428347</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="C7" t="n">
-        <v>31.85967649821749</v>
+        <v>50.00531931581128</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>20.86213871524472</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6213,7 +6213,7 @@
         <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.280537100837761</v>
+        <v>7.26936798059926</v>
       </c>
       <c r="C21" t="n">
-        <v>75.53557242119177</v>
+        <v>76.32836379629224</v>
       </c>
       <c r="D21" t="n">
-        <v>6.370469963233041</v>
+        <v>5.452025985449445</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.450483327529043</v>
+        <v>7.693956758182253</v>
       </c>
       <c r="C2" t="n">
-        <v>10.5115726693706</v>
+        <v>9.350165135246622</v>
       </c>
       <c r="D2" t="n">
-        <v>26.41490373046468</v>
+        <v>34.49272384100744</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.79265561242145</v>
+        <v>22.8059991696534</v>
       </c>
       <c r="C3" t="n">
-        <v>35.15147655055704</v>
+        <v>23.18888077430966</v>
       </c>
       <c r="D3" t="n">
-        <v>65.90963212460962</v>
+        <v>71.64794745593223</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.03665312688917</v>
+        <v>39.3347035183527</v>
       </c>
       <c r="C4" t="n">
-        <v>94.27821378652546</v>
+        <v>62.12892171555515</v>
       </c>
       <c r="D4" t="n">
-        <v>81.54101907162733</v>
+        <v>75.54254059867932</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.64435495581795</v>
+        <v>46.38757902566179</v>
       </c>
       <c r="C5" t="n">
-        <v>109.3176068678824</v>
+        <v>102.199936012093</v>
       </c>
       <c r="D5" t="n">
-        <v>60.77018289287758</v>
+        <v>51.32086123950202</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.8453511932813</v>
+        <v>40.29190752999335</v>
       </c>
       <c r="C6" t="n">
-        <v>88.27188133194348</v>
+        <v>104.4932986492135</v>
       </c>
       <c r="D6" t="n">
-        <v>44.55858305264999</v>
+        <v>39.60762938013333</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="C7" t="n">
-        <v>59.10808402958771</v>
+        <v>82.04465564390594</v>
       </c>
       <c r="D7" t="n">
-        <v>36.89015173477814</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>32.3780392860598</v>
+        <v>48.31671326450677</v>
       </c>
       <c r="D8" t="n">
         <v>33.79666471869644</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>29.06562253193106</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.488263348408196</v>
+        <v>7.47478209390516</v>
       </c>
       <c r="C21" t="n">
-        <v>85.17899558814322</v>
+        <v>85.0256463181712</v>
       </c>
       <c r="D21" t="n">
-        <v>7.488263348408196</v>
+        <v>6.540434332167015</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_82_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_82_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497636829007</v>
+        <v>10.84497643241684</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907206761205</v>
+        <v>37.78907229106032</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.176575718044184</v>
+        <v>5.730461349688632</v>
       </c>
       <c r="C2" t="n">
-        <v>6.732825755724625</v>
+        <v>7.459319056867265</v>
       </c>
       <c r="D2" t="n">
-        <v>30.62365613857076</v>
+        <v>21.79185379116645</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.42097414313941</v>
+        <v>18.30468594568178</v>
       </c>
       <c r="C3" t="n">
-        <v>30.28200793749286</v>
+        <v>15.06982726018854</v>
       </c>
       <c r="D3" t="n">
-        <v>81.23471378790232</v>
+        <v>65.66419519854792</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.32568786256524</v>
+        <v>36.73110860669016</v>
       </c>
       <c r="C4" t="n">
-        <v>59.89544568839366</v>
+        <v>40.58545009356314</v>
       </c>
       <c r="D4" t="n">
-        <v>92.37656848339938</v>
+        <v>71.43294470870217</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.98983233672161</v>
+        <v>48.54742397500478</v>
       </c>
       <c r="C5" t="n">
-        <v>107.5504610002381</v>
+        <v>83.66944809443443</v>
       </c>
       <c r="D5" t="n">
-        <v>64.59899893944014</v>
+        <v>51.95899724726245</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.11960296013142</v>
+        <v>44.63908636439822</v>
       </c>
       <c r="C6" t="n">
-        <v>133.67574915795</v>
+        <v>131.5826630524958</v>
       </c>
       <c r="D6" t="n">
-        <v>46.32965591111124</v>
+        <v>41.0164373357275</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.75230614555609</v>
+        <v>30.3625112492411</v>
       </c>
       <c r="C7" t="n">
-        <v>115.7009304408951</v>
+        <v>148.2193596486622</v>
       </c>
       <c r="D7" t="n">
-        <v>38.92629647338602</v>
+        <v>38.20765715387736</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.10833640483241</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="C8" t="n">
-        <v>78.69198723390308</v>
+        <v>107.4817386609408</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>35.38218726105504</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>44.26405874137593</v>
+        <v>55.35780779936488</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.664533843567649</v>
+        <v>7.672456263560013</v>
       </c>
       <c r="C21" t="n">
-        <v>93.8905395837037</v>
+        <v>94.94664626155517</v>
       </c>
       <c r="D21" t="n">
-        <v>7.664533843567649</v>
+        <v>7.672456263560013</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.409650834578178</v>
+        <v>6.906595099376311</v>
       </c>
       <c r="C2" t="n">
-        <v>7.49171673110741</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="D2" t="n">
-        <v>29.39058102203676</v>
+        <v>19.21280257211008</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.24916829489622</v>
+        <v>18.6679325962531</v>
       </c>
       <c r="C3" t="n">
-        <v>28.01907947920397</v>
+        <v>22.14822820780804</v>
       </c>
       <c r="D3" t="n">
-        <v>86.32998437294327</v>
+        <v>67.13681675491813</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.11246868429443</v>
+        <v>35.79943003535994</v>
       </c>
       <c r="C4" t="n">
-        <v>67.50202690089795</v>
+        <v>38.67104207028186</v>
       </c>
       <c r="D4" t="n">
-        <v>106.9260694603371</v>
+        <v>85.45917415927636</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.74501730546565</v>
+        <v>51.41903600992671</v>
       </c>
       <c r="C5" t="n">
-        <v>107.7222668484813</v>
+        <v>79.27612711792995</v>
       </c>
       <c r="D5" t="n">
-        <v>79.98789420350889</v>
+        <v>62.9791152274329</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.25672884355649</v>
+        <v>54.25923211831272</v>
       </c>
       <c r="C6" t="n">
-        <v>151.225471119066</v>
+        <v>131.5424113966216</v>
       </c>
       <c r="D6" t="n">
-        <v>53.81646390369741</v>
+        <v>47.21519234034186</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.4301950875719</v>
+        <v>41.26187426178919</v>
       </c>
       <c r="C7" t="n">
-        <v>150.3752776071882</v>
+        <v>169.5389927940859</v>
       </c>
       <c r="D7" t="n">
-        <v>42.93869934064274</v>
+        <v>40.78278138211675</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.12078032981814</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="C8" t="n">
-        <v>113.4065860560703</v>
+        <v>149.0391189817083</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.53593643552752</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>68.00468172547228</v>
+        <v>92.1890546718882</v>
       </c>
       <c r="D9" t="n">
         <v>35.49999698556465</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28249096357838</v>
+        <v>47.83074815090461</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.838780255698454</v>
+        <v>7.853066760981997</v>
       </c>
       <c r="C21" t="n">
-        <v>101.9041433240799</v>
+        <v>103.0715012378887</v>
       </c>
       <c r="D21" t="n">
-        <v>8.818627787660761</v>
+        <v>8.834700106104746</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.711448290409448</v>
+        <v>7.837291923002287</v>
       </c>
       <c r="C2" t="n">
-        <v>6.634650985299944</v>
+        <v>8.011061266653973</v>
       </c>
       <c r="D2" t="n">
-        <v>30.93977889933823</v>
+        <v>22.71371488545421</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.46162670964103</v>
+        <v>20.35653864755761</v>
       </c>
       <c r="C3" t="n">
-        <v>28.24488145118073</v>
+        <v>25.58434517267188</v>
       </c>
       <c r="D3" t="n">
-        <v>88.0774952865026</v>
+        <v>66.43486714638166</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.38048580755381</v>
+        <v>34.91880234465055</v>
       </c>
       <c r="C4" t="n">
-        <v>67.70623042338129</v>
+        <v>45.84369079750906</v>
       </c>
       <c r="D4" t="n">
-        <v>119.5611624139936</v>
+        <v>96.53721525399736</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.03387211469246</v>
+        <v>52.10625940289948</v>
       </c>
       <c r="C5" t="n">
-        <v>113.5636656887498</v>
+        <v>75.49639845657973</v>
       </c>
       <c r="D5" t="n">
-        <v>95.64677008624551</v>
+        <v>75.05461198966867</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.53598715991909</v>
+        <v>60.61899374642356</v>
       </c>
       <c r="C6" t="n">
-        <v>160.1210870672463</v>
+        <v>128.4027822384404</v>
       </c>
       <c r="D6" t="n">
-        <v>62.95358978712248</v>
+        <v>54.66174867705392</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>57.13182590093888</v>
+        <v>51.26293812495145</v>
       </c>
       <c r="C7" t="n">
-        <v>178.0428914082718</v>
+        <v>178.5219842879443</v>
       </c>
       <c r="D7" t="n">
-        <v>47.54996830749001</v>
+        <v>43.95677170994669</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.46148784092078</v>
       </c>
       <c r="C8" t="n">
-        <v>148.9556704268473</v>
+        <v>184.0040634684584</v>
       </c>
       <c r="D8" t="n">
-        <v>39.72151211382594</v>
+        <v>39.80496066868692</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.41562343626167</v>
+        <v>15.97499864350409</v>
       </c>
       <c r="C9" t="n">
-        <v>98.73436661610168</v>
+        <v>131.6828013183289</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>56.94136684631501</v>
+        <v>74.02377690020951</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>42.64712027248143</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.997300549697052</v>
+        <v>8.019710716642184</v>
       </c>
       <c r="C21" t="n">
-        <v>108.9632199896223</v>
+        <v>111.2734861934103</v>
       </c>
       <c r="D21" t="n">
-        <v>9.996625687121314</v>
+        <v>10.02463839580273</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.95059381961817</v>
+        <v>7.146141539212532</v>
       </c>
       <c r="C2" t="n">
-        <v>4.564145077043421</v>
+        <v>5.382922662385262</v>
       </c>
       <c r="D2" t="n">
-        <v>25.59710789282709</v>
+        <v>18.68069531640831</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.05129722699487</v>
+        <v>24.45042657426681</v>
       </c>
       <c r="C3" t="n">
-        <v>41.82736093943536</v>
+        <v>36.79590395517045</v>
       </c>
       <c r="D3" t="n">
-        <v>94.44903788706439</v>
+        <v>72.27135724812895</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.84374755077129</v>
+        <v>25.02769422436394</v>
       </c>
       <c r="C4" t="n">
-        <v>93.07851809193585</v>
+        <v>63.20099020859267</v>
       </c>
       <c r="D4" t="n">
-        <v>112.426801847232</v>
+        <v>90.53873678104935</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.47821860962199</v>
+        <v>34.14027641518284</v>
       </c>
       <c r="C5" t="n">
-        <v>95.67131377885168</v>
+        <v>76.72358308688824</v>
       </c>
       <c r="D5" t="n">
-        <v>63.32272692391928</v>
+        <v>53.55433726666352</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.46170882509904</v>
+        <v>31.79880814055419</v>
       </c>
       <c r="C6" t="n">
-        <v>117.2530735613093</v>
+        <v>117.5750868083023</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31578827006476</v>
+        <v>28.94094057349173</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.37385025333556</v>
+        <v>21.4992929753009</v>
       </c>
       <c r="C7" t="n">
-        <v>104.7416808183879</v>
+        <v>129.3550775115597</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>27.96704685087888</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.76762889372977</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>72.76713983877357</v>
+        <v>97.05066930331843</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>43.4874963073167</v>
+        <v>56.46718270516377</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>23.35381438862312</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.353470231257857</v>
+        <v>4.432590884674349</v>
       </c>
       <c r="C2" t="n">
-        <v>2.944261365036184</v>
+        <v>2.465168485363741</v>
       </c>
       <c r="D2" t="n">
-        <v>17.58899186928585</v>
+        <v>12.65767315085412</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>31.21466825652734</v>
+        <v>25.25545969174919</v>
       </c>
       <c r="C3" t="n">
-        <v>30.18874190558942</v>
+        <v>29.20699420134261</v>
       </c>
       <c r="D3" t="n">
-        <v>94.47358157967057</v>
+        <v>70.98035901704439</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.30016242225481</v>
+        <v>34.72736154232243</v>
       </c>
       <c r="C4" t="n">
-        <v>101.9358458796506</v>
+        <v>79.57556016772521</v>
       </c>
       <c r="D4" t="n">
-        <v>129.2480670117968</v>
+        <v>104.4756271905371</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.45429681182157</v>
+        <v>37.77274292089604</v>
       </c>
       <c r="C5" t="n">
-        <v>131.8487166803467</v>
+        <v>96.55488671267382</v>
       </c>
       <c r="D5" t="n">
-        <v>81.68140899333464</v>
+        <v>67.98602851909163</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.94222542083224</v>
+        <v>38.07806645691679</v>
       </c>
       <c r="C6" t="n">
-        <v>136.5738683808866</v>
+        <v>127.6380007768321</v>
       </c>
       <c r="D6" t="n">
-        <v>38.80259626265094</v>
+        <v>35.05919226635785</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.69702517448201</v>
+        <v>20.06201433628357</v>
       </c>
       <c r="C7" t="n">
-        <v>132.3494080095125</v>
+        <v>153.1899482752638</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>30.42239785920016</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>94.54721265748907</v>
+        <v>124.1714496331366</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>28.12216298814988</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>48.7015583645715</v>
+        <v>63.5671821022767</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>35.16129402759952</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.403940274801944</v>
+        <v>4.999059310024759</v>
       </c>
       <c r="C2" t="n">
-        <v>5.972953032637593</v>
+        <v>10.40358042190345</v>
       </c>
       <c r="D2" t="n">
-        <v>27.53213261789755</v>
+        <v>13.99874051485527</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.68113728476482</v>
+        <v>20.27799883121787</v>
       </c>
       <c r="C3" t="n">
-        <v>20.20436775339936</v>
+        <v>18.6826588118168</v>
       </c>
       <c r="D3" t="n">
-        <v>87.23319226085033</v>
+        <v>64.98678928261761</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.15749020996954</v>
+        <v>41.24911154163399</v>
       </c>
       <c r="C4" t="n">
-        <v>89.31351564614933</v>
+        <v>76.10410028550849</v>
       </c>
       <c r="D4" t="n">
-        <v>144.3080767949429</v>
+        <v>115.1324985201362</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.60909415392309</v>
+        <v>44.74315162104839</v>
       </c>
       <c r="C5" t="n">
-        <v>158.6749726988907</v>
+        <v>121.6385405561798</v>
       </c>
       <c r="D5" t="n">
-        <v>104.8261111209532</v>
+        <v>87.59643891142167</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.30198704894308</v>
+        <v>44.71958967614647</v>
       </c>
       <c r="C6" t="n">
-        <v>171.7538156148668</v>
+        <v>141.7260803327738</v>
       </c>
       <c r="D6" t="n">
-        <v>51.96488773348793</v>
+        <v>46.32965591111124</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.53650157707104</v>
+        <v>30.24273802932299</v>
       </c>
       <c r="C7" t="n">
-        <v>162.113053159163</v>
+        <v>170.7966116032261</v>
       </c>
       <c r="D7" t="n">
-        <v>34.19525428662065</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.52143120414207</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C8" t="n">
-        <v>131.5149224609027</v>
+        <v>162.057093540021</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>78.21093085882212</v>
+        <v>102.9499912581375</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>52.10135066437823</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>34.82848155585983</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.845505757534756</v>
+        <v>2.934443887993716</v>
       </c>
       <c r="C2" t="n">
-        <v>2.833323874456295</v>
+        <v>4.808600255400877</v>
       </c>
       <c r="D2" t="n">
-        <v>19.19513111343364</v>
+        <v>9.656470418971628</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.46653544816226</v>
+        <v>20.68051538995906</v>
       </c>
       <c r="C3" t="n">
-        <v>22.78636421556847</v>
+        <v>29.36898257254333</v>
       </c>
       <c r="D3" t="n">
-        <v>90.52204707007715</v>
+        <v>63.98540662428587</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.94351026817274</v>
+        <v>45.95855527890593</v>
       </c>
       <c r="C4" t="n">
-        <v>84.37434294608363</v>
+        <v>73.04104744825845</v>
       </c>
       <c r="D4" t="n">
-        <v>154.4927274787993</v>
+        <v>122.3179099675186</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.44987109938586</v>
+        <v>47.34478303730243</v>
       </c>
       <c r="C5" t="n">
-        <v>185.4766850248287</v>
+        <v>144.292368831675</v>
       </c>
       <c r="D5" t="n">
-        <v>111.0111216577081</v>
+        <v>95.35224577497146</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.01014593887452</v>
+        <v>37.35353665118265</v>
       </c>
       <c r="C6" t="n">
-        <v>205.927471451994</v>
+        <v>181.615471304026</v>
       </c>
       <c r="D6" t="n">
-        <v>50.91834468076083</v>
+        <v>46.08814597586652</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.24061030299848</v>
+        <v>9.342311153612647</v>
       </c>
       <c r="C7" t="n">
-        <v>170.2576321135946</v>
+        <v>192.9546572880766</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>97.55136063248432</v>
+        <v>126.6749062789659</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>39.71562162760046</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.774239085752239</v>
+        <v>3.91815508764902</v>
       </c>
       <c r="C2" t="n">
-        <v>3.047344873982099</v>
+        <v>7.922703973271759</v>
       </c>
       <c r="D2" t="n">
-        <v>15.51946770873358</v>
+        <v>10.28282545428109</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.54168805303276</v>
+        <v>15.32508166329271</v>
       </c>
       <c r="C3" t="n">
-        <v>16.8222469122691</v>
+        <v>23.81229056650639</v>
       </c>
       <c r="D3" t="n">
-        <v>86.0452775387117</v>
+        <v>57.93293202760429</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.41649167744146</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="C4" t="n">
-        <v>71.59886007071988</v>
+        <v>73.84509881803659</v>
       </c>
       <c r="D4" t="n">
-        <v>162.2141731727005</v>
+        <v>125.7766071295801</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.94261063592651</v>
+        <v>57.16226007977055</v>
       </c>
       <c r="C5" t="n">
-        <v>173.131207643925</v>
+        <v>140.9053392520235</v>
       </c>
       <c r="D5" t="n">
-        <v>134.4258044039945</v>
+        <v>113.9318210778424</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.60262283062086</v>
+        <v>48.50324532831367</v>
       </c>
       <c r="C6" t="n">
-        <v>246.6218955407285</v>
+        <v>205.4444515815046</v>
       </c>
       <c r="D6" t="n">
-        <v>67.86429180376503</v>
+        <v>61.78629176677302</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.27781890476862</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="C7" t="n">
-        <v>226.850478524902</v>
+        <v>228.4075303838374</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>37.90822410408209</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>148.7053247622644</v>
+        <v>182.0012981517949</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>63.89999457401638</v>
+        <v>83.6468678972367</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.52209415667683</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.334015203622168</v>
+        <v>2.704714925199963</v>
       </c>
       <c r="C2" t="n">
-        <v>1.926188995732242</v>
+        <v>4.097814917526186</v>
       </c>
       <c r="D2" t="n">
-        <v>10.96710360414112</v>
+        <v>7.324819621385452</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.33413837680919</v>
+        <v>14.67712817848982</v>
       </c>
       <c r="C3" t="n">
-        <v>14.72621556370216</v>
+        <v>27.69510273680253</v>
       </c>
       <c r="D3" t="n">
-        <v>80.34623211555896</v>
+        <v>54.40845776935824</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.80914970141117</v>
+        <v>38.99011007416208</v>
       </c>
       <c r="C4" t="n">
-        <v>60.92922602096554</v>
+        <v>69.39090948386881</v>
       </c>
       <c r="D4" t="n">
-        <v>168.6593468510808</v>
+        <v>126.4913194582718</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.07853378746908</v>
+        <v>62.48824137530949</v>
       </c>
       <c r="C5" t="n">
-        <v>161.9147401229052</v>
+        <v>142.427048193606</v>
       </c>
       <c r="D5" t="n">
-        <v>150.354660905399</v>
+        <v>127.3817646260237</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.54478183152831</v>
+        <v>56.95609306187872</v>
       </c>
       <c r="C6" t="n">
-        <v>270.8936440328225</v>
+        <v>224.4029814982147</v>
       </c>
       <c r="D6" t="n">
-        <v>82.19388129495147</v>
+        <v>73.05675541152641</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.06201433628357</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C7" t="n">
-        <v>273.0230548033337</v>
+        <v>261.405052471277</v>
       </c>
       <c r="D7" t="n">
-        <v>43.95677170994669</v>
+        <v>42.27994663109313</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>191.7647790705294</v>
+        <v>225.6448923440869</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>72.33124385808797</v>
+        <v>98.95624159726147</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.942117943178443</v>
+        <v>3.627557767191965</v>
       </c>
       <c r="C2" t="n">
-        <v>2.741039590257095</v>
+        <v>6.687665361329272</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5131763118806</v>
+        <v>8.49506288484765</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.92747384307275</v>
+        <v>11.98713946885356</v>
       </c>
       <c r="C3" t="n">
-        <v>11.30482481440202</v>
+        <v>21.89297380470387</v>
       </c>
       <c r="D3" t="n">
-        <v>72.13882130805563</v>
+        <v>49.08247647381928</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.90001026954963</v>
+        <v>33.61700488881928</v>
       </c>
       <c r="C4" t="n">
-        <v>50.0936766091935</v>
+        <v>69.09736692029901</v>
       </c>
       <c r="D4" t="n">
-        <v>169.3230082991516</v>
+        <v>123.5814192628842</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.15216486528759</v>
+        <v>61.60466844148736</v>
       </c>
       <c r="C5" t="n">
-        <v>140.4880964777186</v>
+        <v>135.6529890343031</v>
       </c>
       <c r="D5" t="n">
-        <v>169.1551294417254</v>
+        <v>140.1935721664445</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>74.3045567436241</v>
+        <v>67.13976199803088</v>
       </c>
       <c r="C6" t="n">
-        <v>266.5464651984176</v>
+        <v>226.0935510449277</v>
       </c>
       <c r="D6" t="n">
-        <v>101.6354310821511</v>
+        <v>90.36496743739767</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.54890444432775</v>
+        <v>37.36924461445059</v>
       </c>
       <c r="C7" t="n">
-        <v>321.2916624303323</v>
+        <v>292.2466566001905</v>
       </c>
       <c r="D7" t="n">
-        <v>52.70021676396878</v>
+        <v>50.30475236560656</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>260.1091455016712</v>
+        <v>275.7974738155352</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>132.0156137900686</v>
+        <v>168.735923172012</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>49.82369599052563</v>
+        <v>64.34374453633596</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
         <v>11.36962016288231</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.718500450788423</v>
+        <v>5.631304831559704</v>
       </c>
       <c r="C2" t="n">
-        <v>9.101782966072179</v>
+        <v>13.27519245682537</v>
       </c>
       <c r="D2" t="n">
-        <v>14.03015644139117</v>
+        <v>6.065237316836795</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.537236978401258</v>
+        <v>2.569233742013903</v>
       </c>
       <c r="C2" t="n">
-        <v>1.578650308428871</v>
+        <v>3.744385743997335</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6814150222053</v>
+        <v>6.251769380643688</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.10619298297468</v>
+        <v>15.91903902436203</v>
       </c>
       <c r="C3" t="n">
-        <v>12.7283589855599</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D3" t="n">
-        <v>78.26983572107696</v>
+        <v>52.5725895624167</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.28810371236337</v>
+        <v>46.73708120837366</v>
       </c>
       <c r="C4" t="n">
-        <v>73.62813257539804</v>
+        <v>93.88256946171398</v>
       </c>
       <c r="D4" t="n">
-        <v>172.2711966550048</v>
+        <v>128.3036257203114</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.83503499462009</v>
+        <v>40.10439371848221</v>
       </c>
       <c r="C5" t="n">
-        <v>219.1260875878881</v>
+        <v>195.2205309894783</v>
       </c>
       <c r="D5" t="n">
-        <v>152.1463504656495</v>
+        <v>129.2716289566988</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.30570875111504</v>
+        <v>23.18495378349268</v>
       </c>
       <c r="C6" t="n">
-        <v>263.8496042548516</v>
+        <v>241.2281736535965</v>
       </c>
       <c r="D6" t="n">
-        <v>79.98004022187492</v>
+        <v>72.77499382040757</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.647413705455153</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>182.8937068149553</v>
+        <v>193.9128430474215</v>
       </c>
       <c r="D7" t="n">
-        <v>32.39865598784899</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>97.30101496790137</v>
+        <v>124.3383467428585</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>24.78422079371073</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>49.03437083631118</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>23.48831382410494</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
         <v>9.365873098514571</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.58105577219387</v>
+        <v>6.609125544989528</v>
       </c>
       <c r="C2" t="n">
-        <v>4.968625131193107</v>
+        <v>6.606180301876787</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5279025274443</v>
+        <v>13.53731909385927</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.3902779224005</v>
+        <v>11.96259577624738</v>
       </c>
       <c r="C3" t="n">
-        <v>22.93362637120549</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D3" t="n">
-        <v>14.92256510455152</v>
+        <v>8.231954500109506</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39670792053571</v>
+        <v>13.39771505987933</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13570617221635</v>
+        <v>70.14097884289767</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576083284768907</v>
+        <v>1.576201771750509</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.807438581247383</v>
+        <v>5.772676500971245</v>
       </c>
       <c r="C2" t="n">
-        <v>6.210535977065322</v>
+        <v>8.262388678941157</v>
       </c>
       <c r="D2" t="n">
-        <v>18.12600786350886</v>
+        <v>11.97830373951533</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.30530784048753</v>
+        <v>18.47649179392497</v>
       </c>
       <c r="C3" t="n">
-        <v>20.70505908256523</v>
+        <v>28.6424892714007</v>
       </c>
       <c r="D3" t="n">
-        <v>23.51776625523235</v>
+        <v>17.61255381418778</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.95263943048468</v>
+        <v>13.94965312964293</v>
       </c>
       <c r="C4" t="n">
-        <v>35.49312475163494</v>
+        <v>51.51033854642165</v>
       </c>
       <c r="D4" t="n">
-        <v>22.89631995844411</v>
+        <v>19.38657191576176</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4896,7 +4896,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43738851842041</v>
+        <v>15.4386237634868</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12437805013492</v>
+        <v>86.13126941734744</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249976530193771</v>
+        <v>3.250236581786696</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.68864710903352</v>
+        <v>6.277294820954105</v>
       </c>
       <c r="C2" t="n">
-        <v>8.609927366244527</v>
+        <v>4.478733026773948</v>
       </c>
       <c r="D2" t="n">
-        <v>15.30937370002476</v>
+        <v>14.39733008277947</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.03180114163017</v>
+        <v>19.34042977366217</v>
       </c>
       <c r="C3" t="n">
-        <v>22.75200304591983</v>
+        <v>30.71397692736146</v>
       </c>
       <c r="D3" t="n">
-        <v>32.55966261134547</v>
+        <v>23.10543221944868</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.76190263842031</v>
+        <v>26.34225440035042</v>
       </c>
       <c r="C4" t="n">
-        <v>44.61846966260904</v>
+        <v>62.71600684269474</v>
       </c>
       <c r="D4" t="n">
-        <v>29.53293443915255</v>
+        <v>23.86628669023996</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.12520604225386</v>
+        <v>12.27184630308513</v>
       </c>
       <c r="C5" t="n">
-        <v>39.71169463678348</v>
+        <v>56.54866776461629</v>
       </c>
       <c r="D5" t="n">
-        <v>30.87596529856219</v>
+        <v>29.64878066825368</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5207,7 +5207,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5263,7 +5263,7 @@
         <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5319,7 +5319,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72700198391217</v>
+        <v>16.72812763616163</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0347121018642</v>
+        <v>102.0415785805859</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181750495978043</v>
+        <v>4.182031909040408</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.127087422204344</v>
+        <v>5.939573610693203</v>
       </c>
       <c r="C2" t="n">
-        <v>8.151451188361266</v>
+        <v>2.76067454434203</v>
       </c>
       <c r="D2" t="n">
-        <v>26.75557018383832</v>
+        <v>20.0374706436774</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.89926520155685</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="C3" t="n">
-        <v>28.89283493598363</v>
+        <v>23.12015843501239</v>
       </c>
       <c r="D3" t="n">
-        <v>36.95298358784994</v>
+        <v>28.90756115154733</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.81143199198916</v>
+        <v>32.04719030972863</v>
       </c>
       <c r="C4" t="n">
-        <v>51.49757582626644</v>
+        <v>69.85036740945631</v>
       </c>
       <c r="D4" t="n">
-        <v>38.68380479043707</v>
+        <v>29.73713796163589</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.64311116620645</v>
+        <v>25.86905200690346</v>
       </c>
       <c r="C5" t="n">
-        <v>62.75822199397737</v>
+        <v>88.57818661566847</v>
       </c>
       <c r="D5" t="n">
-        <v>34.11573272257667</v>
+        <v>31.26866438026092</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.68556299720054</v>
+        <v>11.14970867713103</v>
       </c>
       <c r="C6" t="n">
-        <v>38.40007970390975</v>
+        <v>52.28690098048088</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
         <v>39.52516257297658</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
         <v>39.8884092235479</v>
@@ -5546,7 +5546,7 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
         <v>42.15624642035802</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5574,7 +5574,7 @@
         <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.74489413227862</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04747852279032</v>
+        <v>18.04716022433317</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7383122677273</v>
+        <v>117.7362357492211</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01582617426344</v>
+        <v>6.015720074777721</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.721044783273664</v>
+        <v>6.449100669197297</v>
       </c>
       <c r="C2" t="n">
-        <v>5.608724634362028</v>
+        <v>5.20817157102933</v>
       </c>
       <c r="D2" t="n">
-        <v>34.08824378685775</v>
+        <v>23.32828894831271</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.57114048416017</v>
+        <v>18.28505099159684</v>
       </c>
       <c r="C3" t="n">
-        <v>28.55904071653972</v>
+        <v>15.12382338392211</v>
       </c>
       <c r="D3" t="n">
-        <v>46.15686831516379</v>
+        <v>35.47054455443726</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.12001956629214</v>
+        <v>26.04871183678062</v>
       </c>
       <c r="C4" t="n">
-        <v>52.21228815495812</v>
+        <v>52.28886447588937</v>
       </c>
       <c r="D4" t="n">
-        <v>41.82343394861837</v>
+        <v>32.36625831360885</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.68528525976006</v>
+        <v>22.50656611985813</v>
       </c>
       <c r="C5" t="n">
-        <v>59.51845456996289</v>
+        <v>81.95138961200252</v>
       </c>
       <c r="D5" t="n">
-        <v>32.15223731408305</v>
+        <v>27.93072218582176</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.77864910265474</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="C6" t="n">
-        <v>47.05418571684538</v>
+        <v>66.1334706011779</v>
       </c>
       <c r="D6" t="n">
-        <v>31.51704654943536</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>24.73316991308989</v>
+        <v>30.60205768907732</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5840,7 +5840,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
         <v>18.60902773399829</v>
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
         <v>30.28593492830985</v>
@@ -5882,7 +5882,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>3.553926689373453</v>
       </c>
       <c r="C11" t="n">
         <v>20.25738212942868</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>31.89403766786613</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.05062000811281</v>
+        <v>7.050377601959345</v>
       </c>
       <c r="C21" t="n">
-        <v>66.98089007707169</v>
+        <v>66.97858721861377</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406637505070506</v>
+        <v>4.40648600122459</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.806456833543137</v>
+        <v>5.116869034534376</v>
       </c>
       <c r="C2" t="n">
-        <v>5.767767762450011</v>
+        <v>3.319288988058466</v>
       </c>
       <c r="D2" t="n">
-        <v>28.47264691856599</v>
+        <v>29.86280166777948</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.98133109808609</v>
+        <v>20.89159114637213</v>
       </c>
       <c r="C3" t="n">
-        <v>24.32770811123596</v>
+        <v>18.49612674800991</v>
       </c>
       <c r="D3" t="n">
-        <v>63.63688618927824</v>
+        <v>46.49557127312895</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.36549755008285</v>
+        <v>31.93232582833176</v>
       </c>
       <c r="C4" t="n">
-        <v>63.73702445511142</v>
+        <v>43.35496036724339</v>
       </c>
       <c r="D4" t="n">
-        <v>56.30912132478006</v>
+        <v>43.13799412460484</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.69911184307752</v>
+        <v>32.34858685493241</v>
       </c>
       <c r="C5" t="n">
-        <v>82.22137023067039</v>
+        <v>91.13073064671019</v>
       </c>
       <c r="D5" t="n">
-        <v>40.12893741108838</v>
+        <v>33.99301425954582</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.2566624236317</v>
+        <v>22.86294053649972</v>
       </c>
       <c r="C6" t="n">
-        <v>75.10958986110649</v>
+        <v>103.97002712285</v>
       </c>
       <c r="D6" t="n">
-        <v>35.13969557810609</v>
+        <v>33.16736444027425</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.23494080095125</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="C7" t="n">
-        <v>50.00531931581128</v>
+        <v>68.45039518320036</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>27.12078032981814</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
         <v>31.61718481526852</v>
@@ -6182,7 +6182,7 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
         <v>33.45305302221006</v>
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.26936798059926</v>
+        <v>7.270643927477344</v>
       </c>
       <c r="C21" t="n">
-        <v>76.32836379629224</v>
+        <v>76.34176123851211</v>
       </c>
       <c r="D21" t="n">
-        <v>5.452025985449445</v>
+        <v>5.452982945608007</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.693956758182253</v>
+        <v>5.197372346282614</v>
       </c>
       <c r="C2" t="n">
-        <v>9.350165135246622</v>
+        <v>3.879866927183394</v>
       </c>
       <c r="D2" t="n">
-        <v>34.49272384100744</v>
+        <v>26.04674834137213</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.8059991696534</v>
+        <v>19.10481032464293</v>
       </c>
       <c r="C3" t="n">
-        <v>23.18888077430966</v>
+        <v>15.15818455357075</v>
       </c>
       <c r="D3" t="n">
-        <v>71.64794745593223</v>
+        <v>59.59699438630262</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3347035183527</v>
+        <v>37.088464771036</v>
       </c>
       <c r="C4" t="n">
-        <v>62.12892171555515</v>
+        <v>44.66952054322987</v>
       </c>
       <c r="D4" t="n">
-        <v>75.54254059867932</v>
+        <v>56.74305381005714</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.38757902566179</v>
+        <v>40.71798603363646</v>
       </c>
       <c r="C5" t="n">
-        <v>102.199936012093</v>
+        <v>84.97026380256145</v>
       </c>
       <c r="D5" t="n">
-        <v>51.32086123950202</v>
+        <v>41.55247158224626</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.29190752999335</v>
+        <v>34.37491411649783</v>
       </c>
       <c r="C6" t="n">
-        <v>104.4932986492135</v>
+        <v>126.7927160034756</v>
       </c>
       <c r="D6" t="n">
-        <v>39.60762938013333</v>
+        <v>36.79001346894498</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.13430381349934</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>82.04465564390594</v>
+        <v>113.1856928226148</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>48.31671326450677</v>
+        <v>63.00365892003904</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.62976760897448</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>29.06562253193106</v>
+        <v>32.17187226816797</v>
       </c>
       <c r="D9" t="n">
         <v>33.05937219280708</v>
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6535,7 +6535,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.47478209390516</v>
+        <v>7.478157129136349</v>
       </c>
       <c r="C21" t="n">
-        <v>85.0256463181712</v>
+        <v>85.99880698506801</v>
       </c>
       <c r="D21" t="n">
-        <v>6.540434332167015</v>
+        <v>6.543387487994305</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_82_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_82_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497643241684</v>
+        <v>10.84497611169555</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907229106032</v>
+        <v>37.78907117351432</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.730461349688632</v>
+        <v>0.7579092276785376</v>
       </c>
       <c r="C2" t="n">
-        <v>7.459319056867265</v>
+        <v>3.28394607070558</v>
       </c>
       <c r="D2" t="n">
-        <v>21.79185379116645</v>
+        <v>12.93452600345173</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.30468594568178</v>
+        <v>7.314020396638738</v>
       </c>
       <c r="C3" t="n">
-        <v>15.06982726018854</v>
+        <v>40.83088701962485</v>
       </c>
       <c r="D3" t="n">
-        <v>65.66419519854792</v>
+        <v>53.5101586199724</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.73110860669016</v>
+        <v>13.83478864824605</v>
       </c>
       <c r="C4" t="n">
-        <v>40.58545009356314</v>
+        <v>120.0461457798915</v>
       </c>
       <c r="D4" t="n">
-        <v>71.43294470870217</v>
+        <v>67.31058609856981</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.54742397500478</v>
+        <v>13.05724446648258</v>
       </c>
       <c r="C5" t="n">
-        <v>83.66944809443443</v>
+        <v>125.4182692175301</v>
       </c>
       <c r="D5" t="n">
-        <v>51.95899724726245</v>
+        <v>48.64559874542947</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.63908636439822</v>
+        <v>9.378635818669782</v>
       </c>
       <c r="C6" t="n">
-        <v>131.5826630524958</v>
+        <v>81.8316163920844</v>
       </c>
       <c r="D6" t="n">
-        <v>41.0164373357275</v>
+        <v>30.02773528209295</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.3625112492411</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>148.2193596486622</v>
+        <v>47.01098881785852</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20765715387736</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.93729132011522</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>107.4817386609408</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>35.38218726105504</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>55.35780779936488</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.65583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.672456263560013</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.94664626155517</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.672456263560013</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.906595099376311</v>
+        <v>1.682715565079033</v>
       </c>
       <c r="C2" t="n">
-        <v>7.665486074759095</v>
+        <v>7.297330685666541</v>
       </c>
       <c r="D2" t="n">
-        <v>19.21280257211008</v>
+        <v>12.65865489855837</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6679325962531</v>
+        <v>4.786020058203201</v>
       </c>
       <c r="C3" t="n">
-        <v>22.14822820780804</v>
+        <v>24.47006152835175</v>
       </c>
       <c r="D3" t="n">
-        <v>67.13681675491813</v>
+        <v>51.43867096401163</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.79943003535994</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="C4" t="n">
-        <v>38.67104207028186</v>
+        <v>111.0994789510903</v>
       </c>
       <c r="D4" t="n">
-        <v>85.45917415927636</v>
+        <v>78.3631017529804</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.41903600992671</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="C5" t="n">
-        <v>79.27612711792995</v>
+        <v>177.450897542611</v>
       </c>
       <c r="D5" t="n">
-        <v>62.9791152274329</v>
+        <v>61.11379458936396</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.25923211831272</v>
+        <v>13.44405306195583</v>
       </c>
       <c r="C6" t="n">
-        <v>131.5424113966216</v>
+        <v>143.5776565029833</v>
       </c>
       <c r="D6" t="n">
-        <v>47.21519234034186</v>
+        <v>37.71580155404972</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.26187426178919</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>169.5389927940859</v>
+        <v>83.30227445304611</v>
       </c>
       <c r="D7" t="n">
-        <v>40.78278138211675</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.03180114163017</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>149.0391189817083</v>
+        <v>46.31394794784328</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>92.1890546718882</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>47.83074815090461</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>29.19226798577891</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.853066760981997</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103.0715012378887</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.834700106104746</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.837291923002287</v>
+        <v>0.8933904108645975</v>
       </c>
       <c r="C2" t="n">
-        <v>8.011061266653973</v>
+        <v>3.078760800517997</v>
       </c>
       <c r="D2" t="n">
-        <v>22.71371488545421</v>
+        <v>8.675704462429064</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.35653864755761</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C3" t="n">
-        <v>25.58434517267188</v>
+        <v>28.10252803406495</v>
       </c>
       <c r="D3" t="n">
-        <v>66.43486714638166</v>
+        <v>51.54175447295754</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.91880234465055</v>
+        <v>15.37907778702628</v>
       </c>
       <c r="C4" t="n">
-        <v>45.84369079750906</v>
+        <v>101.2211335509589</v>
       </c>
       <c r="D4" t="n">
-        <v>96.53721525399736</v>
+        <v>85.58680136082843</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.10625940289948</v>
+        <v>17.10695374650068</v>
       </c>
       <c r="C5" t="n">
-        <v>75.49639845657973</v>
+        <v>209.0386299267522</v>
       </c>
       <c r="D5" t="n">
-        <v>75.05461198966867</v>
+        <v>67.91239744127311</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.61899374642356</v>
+        <v>11.10945702125691</v>
       </c>
       <c r="C6" t="n">
-        <v>128.4027822384404</v>
+        <v>186.2444117295497</v>
       </c>
       <c r="D6" t="n">
-        <v>54.66174867705392</v>
+        <v>38.35982804803563</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.26293812495145</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>178.5219842879443</v>
+        <v>80.42771717501144</v>
       </c>
       <c r="D7" t="n">
-        <v>43.95677170994669</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.46148784092078</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>184.0040634684584</v>
+        <v>42.22496875965531</v>
       </c>
       <c r="D8" t="n">
-        <v>39.80496066868692</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.97499864350409</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>131.6828013183289</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>74.02377690020951</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>42.64712027248143</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.019710716642184</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111.2734861934103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.02463839580273</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.146141539212532</v>
+        <v>0.8865181769348698</v>
       </c>
       <c r="C2" t="n">
-        <v>5.382922662385262</v>
+        <v>5.049128442941345</v>
       </c>
       <c r="D2" t="n">
-        <v>18.68069531640831</v>
+        <v>10.389835954044</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.45042657426681</v>
+        <v>4.275511251994859</v>
       </c>
       <c r="C3" t="n">
-        <v>36.79590395517045</v>
+        <v>19.03608798534566</v>
       </c>
       <c r="D3" t="n">
-        <v>72.27135724812895</v>
+        <v>47.16315971201677</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.02769422436394</v>
+        <v>13.29875440172729</v>
       </c>
       <c r="C4" t="n">
-        <v>63.20099020859267</v>
+        <v>85.21668247632739</v>
       </c>
       <c r="D4" t="n">
-        <v>90.53873678104935</v>
+        <v>91.34278815082747</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.14027641518284</v>
+        <v>20.17491532227196</v>
       </c>
       <c r="C5" t="n">
-        <v>76.72358308688824</v>
+        <v>199.5156771955581</v>
       </c>
       <c r="D5" t="n">
-        <v>53.55433726666352</v>
+        <v>81.60777791551612</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.79880814055419</v>
+        <v>16.38242394076653</v>
       </c>
       <c r="C6" t="n">
-        <v>117.5750868083023</v>
+        <v>261.635763181775</v>
       </c>
       <c r="D6" t="n">
-        <v>28.94094057349173</v>
+        <v>49.42903341341842</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.4992929753009</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>129.3550775115597</v>
+        <v>168.7005802546591</v>
       </c>
       <c r="D7" t="n">
-        <v>27.96704685087888</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>97.05066930331843</v>
+        <v>71.09816874155401</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>56.46718270516377</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.35381438862312</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.432590884674349</v>
+        <v>0.5998478472948011</v>
       </c>
       <c r="C2" t="n">
-        <v>2.465168485363741</v>
+        <v>3.412555019961913</v>
       </c>
       <c r="D2" t="n">
-        <v>12.65767315085412</v>
+        <v>8.421431807029139</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.25545969174919</v>
+        <v>3.784637399871454</v>
       </c>
       <c r="C3" t="n">
-        <v>29.20699420134261</v>
+        <v>19.60059291528757</v>
       </c>
       <c r="D3" t="n">
-        <v>70.98035901704439</v>
+        <v>45.54818473853077</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.72736154232243</v>
+        <v>11.57578718077414</v>
       </c>
       <c r="C4" t="n">
-        <v>79.57556016772521</v>
+        <v>69.42919764433444</v>
       </c>
       <c r="D4" t="n">
-        <v>104.4756271905371</v>
+        <v>93.94638306249003</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.77274292089604</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="C5" t="n">
-        <v>96.55488671267382</v>
+        <v>188.2992096745382</v>
       </c>
       <c r="D5" t="n">
-        <v>67.98602851909163</v>
+        <v>92.40700266223104</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.07806645691679</v>
+        <v>19.8843180018149</v>
       </c>
       <c r="C6" t="n">
-        <v>127.6380007768321</v>
+        <v>298.2647700272235</v>
       </c>
       <c r="D6" t="n">
-        <v>35.05919226635785</v>
+        <v>57.88188114698346</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.06201433628357</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>153.1899482752638</v>
+        <v>242.8402033839698</v>
       </c>
       <c r="D7" t="n">
-        <v>30.42239785920016</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>124.1714496331366</v>
+        <v>109.7348496421872</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>63.5671821022767</v>
+        <v>49.58905828921062</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>35.16129402759952</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.999059310024759</v>
+        <v>0.724529805734146</v>
       </c>
       <c r="C2" t="n">
-        <v>10.40358042190345</v>
+        <v>8.175994880967437</v>
       </c>
       <c r="D2" t="n">
-        <v>13.99874051485527</v>
+        <v>15.57640907557989</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.27799883121787</v>
+        <v>2.915790681613027</v>
       </c>
       <c r="C3" t="n">
-        <v>18.6826588118168</v>
+        <v>16.4197303535279</v>
       </c>
       <c r="D3" t="n">
-        <v>64.98678928261761</v>
+        <v>42.01880174176349</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.24911154163399</v>
+        <v>9.457175635009525</v>
       </c>
       <c r="C4" t="n">
-        <v>76.10410028550849</v>
+        <v>59.29559784109885</v>
       </c>
       <c r="D4" t="n">
-        <v>115.1324985201362</v>
+        <v>95.08226515630358</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.74315162104839</v>
+        <v>20.02765316663493</v>
       </c>
       <c r="C5" t="n">
-        <v>121.6385405561798</v>
+        <v>159.6567204031376</v>
       </c>
       <c r="D5" t="n">
-        <v>87.59643891142167</v>
+        <v>103.1325963311275</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.71958967614647</v>
+        <v>23.78872862160447</v>
       </c>
       <c r="C6" t="n">
-        <v>141.7260803327738</v>
+        <v>299.9955912298107</v>
       </c>
       <c r="D6" t="n">
-        <v>46.32965591111124</v>
+        <v>70.60140440320514</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.24273802932299</v>
+        <v>14.19312656029614</v>
       </c>
       <c r="C7" t="n">
-        <v>170.7966116032261</v>
+        <v>329.7356744345592</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>45.57371017884118</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.10280577150543</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>162.057093540021</v>
+        <v>200.3599802212103</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>41.72427743048944</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>102.9499912581375</v>
+        <v>84.86718029361549</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>43.26562132615692</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>52.10135066437823</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>34.82848155585983</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.934443887993716</v>
+        <v>0.491855599827652</v>
       </c>
       <c r="C2" t="n">
-        <v>4.808600255400877</v>
+        <v>4.316744655573225</v>
       </c>
       <c r="D2" t="n">
-        <v>9.656470418971628</v>
+        <v>11.34016773175491</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.68051538995906</v>
+        <v>3.971169463678348</v>
       </c>
       <c r="C3" t="n">
-        <v>29.36898257254333</v>
+        <v>24.35716054236337</v>
       </c>
       <c r="D3" t="n">
-        <v>63.98540662428587</v>
+        <v>47.69821221083129</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.95855527890593</v>
+        <v>14.25595841336793</v>
       </c>
       <c r="C4" t="n">
-        <v>73.04104744825845</v>
+        <v>85.79100488331179</v>
       </c>
       <c r="D4" t="n">
-        <v>122.3179099675186</v>
+        <v>98.55372503852031</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.34478303730243</v>
+        <v>14.67712817848982</v>
       </c>
       <c r="C5" t="n">
-        <v>144.292368831675</v>
+        <v>246.5904796141926</v>
       </c>
       <c r="D5" t="n">
-        <v>95.35224577497146</v>
+        <v>96.89849840916021</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.35353665118265</v>
+        <v>8.774860980557992</v>
       </c>
       <c r="C6" t="n">
-        <v>181.615471304026</v>
+        <v>287.7188361882043</v>
       </c>
       <c r="D6" t="n">
-        <v>46.08814597586652</v>
+        <v>61.102013616913</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.342311153612647</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>192.9546572880766</v>
+        <v>140.8533066236984</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>126.6749062789659</v>
+        <v>62.50296759087318</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>39.71562162760046</v>
+        <v>33.05937219280708</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>26.40312275801371</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>34.75877746885832</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.91815508764902</v>
+        <v>0.2984513020910303</v>
       </c>
       <c r="C2" t="n">
-        <v>7.922703973271759</v>
+        <v>3.198534020436108</v>
       </c>
       <c r="D2" t="n">
-        <v>10.28282545428109</v>
+        <v>8.423395302437633</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.32508166329271</v>
+        <v>2.842159603794516</v>
       </c>
       <c r="C3" t="n">
-        <v>23.81229056650639</v>
+        <v>20.30745126234527</v>
       </c>
       <c r="D3" t="n">
-        <v>57.93293202760429</v>
+        <v>45.57272843113694</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.44429940832985</v>
+        <v>10.26122700478766</v>
       </c>
       <c r="C4" t="n">
-        <v>73.84509881803659</v>
+        <v>69.90141829007715</v>
       </c>
       <c r="D4" t="n">
-        <v>125.7766071295801</v>
+        <v>95.80974020515048</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.16226007977055</v>
+        <v>14.08807955594173</v>
       </c>
       <c r="C5" t="n">
-        <v>140.9053392520235</v>
+        <v>184.9121800948868</v>
       </c>
       <c r="D5" t="n">
-        <v>113.9318210778424</v>
+        <v>99.18106182153404</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.50324532831367</v>
+        <v>8.533351045313278</v>
       </c>
       <c r="C6" t="n">
-        <v>205.4444515815046</v>
+        <v>279.3867434222616</v>
       </c>
       <c r="D6" t="n">
-        <v>61.78629176677302</v>
+        <v>63.15484806649307</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.02020009562846</v>
+        <v>3.233876937788993</v>
       </c>
       <c r="C7" t="n">
-        <v>228.4075303838374</v>
+        <v>186.965996292171</v>
       </c>
       <c r="D7" t="n">
-        <v>37.90822410408209</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>182.0012981517949</v>
+        <v>72.76713983877357</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>83.6468678972367</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>34.73423377625215</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.704714925199963</v>
+        <v>0.2395464398362217</v>
       </c>
       <c r="C2" t="n">
-        <v>4.097814917526186</v>
+        <v>11.85951226730147</v>
       </c>
       <c r="D2" t="n">
-        <v>7.324819621385452</v>
+        <v>13.45092529588555</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.67712817848982</v>
+        <v>1.855503161026472</v>
       </c>
       <c r="C3" t="n">
-        <v>27.69510273680253</v>
+        <v>15.60487975900305</v>
       </c>
       <c r="D3" t="n">
-        <v>54.40845776935824</v>
+        <v>42.17588137444298</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.99011007416208</v>
+        <v>7.759733854366789</v>
       </c>
       <c r="C4" t="n">
-        <v>69.39090948386881</v>
+        <v>59.58914040466865</v>
       </c>
       <c r="D4" t="n">
-        <v>126.4913194582718</v>
+        <v>96.10328276872026</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.48824137530949</v>
+        <v>15.09437095279471</v>
       </c>
       <c r="C5" t="n">
-        <v>142.427048193606</v>
+        <v>154.4043701854171</v>
       </c>
       <c r="D5" t="n">
-        <v>127.3817646260237</v>
+        <v>111.6738013580747</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.95609306187872</v>
+        <v>13.76606630894878</v>
       </c>
       <c r="C6" t="n">
-        <v>224.4029814982147</v>
+        <v>291.1804785933786</v>
       </c>
       <c r="D6" t="n">
-        <v>73.05675541152641</v>
+        <v>79.45676869551137</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>261.405052471277</v>
+        <v>298.9539569156047</v>
       </c>
       <c r="D7" t="n">
-        <v>42.27994663109313</v>
+        <v>43.71722527011047</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>225.6448923440869</v>
+        <v>161.7232993205771</v>
       </c>
       <c r="D8" t="n">
-        <v>35.21529015133309</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>98.95624159726147</v>
+        <v>60.23905738488002</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>22.85312305945724</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>35.44600086183109</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.627557767191965</v>
+        <v>0.1325359400733194</v>
       </c>
       <c r="C2" t="n">
-        <v>6.687665361329272</v>
+        <v>12.95317920983241</v>
       </c>
       <c r="D2" t="n">
-        <v>8.49506288484765</v>
+        <v>13.25948449355742</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.98713946885356</v>
+        <v>1.305724446648258</v>
       </c>
       <c r="C3" t="n">
-        <v>21.89297380470387</v>
+        <v>32.18168974521045</v>
       </c>
       <c r="D3" t="n">
-        <v>49.08247647381928</v>
+        <v>42.88273972150068</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.61700488881928</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C4" t="n">
-        <v>69.09736692029901</v>
+        <v>48.66425195181014</v>
       </c>
       <c r="D4" t="n">
-        <v>123.5814192628842</v>
+        <v>95.51619764158067</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.60466844148736</v>
+        <v>13.69538047424301</v>
       </c>
       <c r="C5" t="n">
-        <v>135.6529890343031</v>
+        <v>131.7014545247096</v>
       </c>
       <c r="D5" t="n">
-        <v>140.1935721664445</v>
+        <v>119.1350839103505</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.13976199803088</v>
+        <v>17.02645043475243</v>
       </c>
       <c r="C6" t="n">
-        <v>226.0935510449277</v>
+        <v>270.3301208505848</v>
       </c>
       <c r="D6" t="n">
-        <v>90.36496743739767</v>
+        <v>95.27566945404023</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.36924461445059</v>
+        <v>10.95924962250714</v>
       </c>
       <c r="C7" t="n">
-        <v>292.2466566001905</v>
+        <v>360.6371651734318</v>
       </c>
       <c r="D7" t="n">
-        <v>50.30475236560656</v>
+        <v>54.91602133245383</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>275.7974738155352</v>
+        <v>274.0450541634546</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>168.735923172012</v>
+        <v>125.3593643552752</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>24.73906039931537</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>64.34374453633596</v>
+        <v>47.40368789955724</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.631304831559704</v>
+        <v>3.09643225919444</v>
       </c>
       <c r="C2" t="n">
-        <v>13.27519245682537</v>
+        <v>11.67887068972006</v>
       </c>
       <c r="D2" t="n">
-        <v>6.065237316836795</v>
+        <v>14.78708392136546</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.569233742013903</v>
+        <v>0.207148765596077</v>
       </c>
       <c r="C2" t="n">
-        <v>3.744385743997335</v>
+        <v>12.94532522819844</v>
       </c>
       <c r="D2" t="n">
-        <v>6.251769380643688</v>
+        <v>13.67083678163683</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.91903902436203</v>
+        <v>0.8835729338221294</v>
       </c>
       <c r="C3" t="n">
-        <v>26.51700549170635</v>
+        <v>40.7228947721577</v>
       </c>
       <c r="D3" t="n">
-        <v>52.5725895624167</v>
+        <v>43.06436304678634</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.73708120837366</v>
+        <v>4.09683316982194</v>
       </c>
       <c r="C4" t="n">
-        <v>93.88256946171398</v>
+        <v>62.97126124579891</v>
       </c>
       <c r="D4" t="n">
-        <v>128.3036257203114</v>
+        <v>95.05673971599317</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.10439371848221</v>
+        <v>11.60916660271853</v>
       </c>
       <c r="C5" t="n">
-        <v>195.2205309894783</v>
+        <v>112.1155878249858</v>
       </c>
       <c r="D5" t="n">
-        <v>129.2716289566988</v>
+        <v>123.6511233498858</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.18495378349268</v>
+        <v>17.67047692873834</v>
       </c>
       <c r="C6" t="n">
-        <v>241.2281736535965</v>
+        <v>244.8508226822673</v>
       </c>
       <c r="D6" t="n">
-        <v>72.77499382040757</v>
+        <v>108.3977092690031</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.707300315414209</v>
+        <v>14.85187926984575</v>
       </c>
       <c r="C7" t="n">
-        <v>193.9128430474215</v>
+        <v>374.0517658042602</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>65.6956111250838</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>124.3383467428585</v>
+        <v>365.6715674008095</v>
       </c>
       <c r="D8" t="n">
-        <v>24.78422079371073</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>49.03437083631118</v>
+        <v>215.3296692155656</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>23.48831382410494</v>
+        <v>89.54029936583035</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>22.49183990429443</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>36.07235589714055</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.609125544989528</v>
+        <v>3.73064127613788</v>
       </c>
       <c r="C2" t="n">
-        <v>6.606180301876787</v>
+        <v>8.13476147738907</v>
       </c>
       <c r="D2" t="n">
-        <v>13.53731909385927</v>
+        <v>21.40406344798896</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.96259577624738</v>
+        <v>5.0020045531375</v>
       </c>
       <c r="C3" t="n">
-        <v>33.45305302221006</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="D3" t="n">
-        <v>8.231954500109506</v>
+        <v>13.08669689760998</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39771505987933</v>
+        <v>11.67736893372996</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14097884289767</v>
+        <v>59.94382719314715</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576201771750509</v>
+        <v>0.7784912622486643</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.772676500971245</v>
+        <v>2.178498155723672</v>
       </c>
       <c r="C2" t="n">
-        <v>8.262388678941157</v>
+        <v>5.628359588446964</v>
       </c>
       <c r="D2" t="n">
-        <v>11.97830373951533</v>
+        <v>16.8978414854961</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.47649179392497</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C3" t="n">
-        <v>28.6424892714007</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D3" t="n">
-        <v>17.61255381418778</v>
+        <v>28.63267179435823</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.94965312964293</v>
+        <v>6.35583463729385</v>
       </c>
       <c r="C4" t="n">
-        <v>51.51033854642165</v>
+        <v>38.00738062221102</v>
       </c>
       <c r="D4" t="n">
-        <v>19.38657191576176</v>
+        <v>21.17335273749096</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.154175447295755</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4386237634868</v>
+        <v>13.62682928718404</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13126941734744</v>
+        <v>73.74519378946655</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250236581786696</v>
+        <v>1.603156386727534</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.277294820954105</v>
+        <v>2.055779692692821</v>
       </c>
       <c r="C2" t="n">
-        <v>4.478733026773948</v>
+        <v>8.823948365770333</v>
       </c>
       <c r="D2" t="n">
-        <v>14.39733008277947</v>
+        <v>13.75428533649781</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.34042977366217</v>
+        <v>8.62465358180823</v>
       </c>
       <c r="C3" t="n">
-        <v>30.71397692736146</v>
+        <v>24.49460522095792</v>
       </c>
       <c r="D3" t="n">
-        <v>23.10543221944868</v>
+        <v>35.90742228282709</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.34225440035042</v>
+        <v>14.23043297305752</v>
       </c>
       <c r="C4" t="n">
-        <v>62.71600684269474</v>
+        <v>59.29559784109885</v>
       </c>
       <c r="D4" t="n">
-        <v>23.86628669023996</v>
+        <v>31.26866438026091</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.27184630308513</v>
+        <v>6.381360077604269</v>
       </c>
       <c r="C5" t="n">
-        <v>56.54866776461629</v>
+        <v>44.17864669110647</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>27.56256679672921</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72812763616163</v>
+        <v>14.83584106531234</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0415785805859</v>
+        <v>87.36661960683932</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182031909040408</v>
+        <v>2.472640177552056</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.939573610693203</v>
+        <v>1.93306122966197</v>
       </c>
       <c r="C2" t="n">
-        <v>2.76067454434203</v>
+        <v>5.236642254452487</v>
       </c>
       <c r="D2" t="n">
-        <v>20.0374706436774</v>
+        <v>13.8671863224862</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.44489594093983</v>
+        <v>7.775441817634739</v>
       </c>
       <c r="C3" t="n">
-        <v>23.12015843501239</v>
+        <v>30.46363126277852</v>
       </c>
       <c r="D3" t="n">
-        <v>28.90756115154733</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.04719030972863</v>
+        <v>15.65985763044087</v>
       </c>
       <c r="C4" t="n">
-        <v>69.85036740945631</v>
+        <v>60.54634441630929</v>
       </c>
       <c r="D4" t="n">
-        <v>29.73713796163589</v>
+        <v>42.23184099358505</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.86905200690346</v>
+        <v>14.35806017460961</v>
       </c>
       <c r="C5" t="n">
-        <v>88.57818661566847</v>
+        <v>81.4605157598791</v>
       </c>
       <c r="D5" t="n">
-        <v>31.26866438026092</v>
+        <v>32.39767424014475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.14970867713103</v>
+        <v>6.722026530977913</v>
       </c>
       <c r="C6" t="n">
-        <v>52.28690098048088</v>
+        <v>42.98876847355934</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>33.89189424600839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.13486895504285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04716022433317</v>
+        <v>16.07706987612099</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7362357492211</v>
+        <v>101.5393886912905</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015720074777721</v>
+        <v>3.384646289709682</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.449100669197297</v>
+        <v>1.688606051304514</v>
       </c>
       <c r="C2" t="n">
-        <v>5.20817157102933</v>
+        <v>11.42852502513712</v>
       </c>
       <c r="D2" t="n">
-        <v>23.32828894831271</v>
+        <v>15.05706454003333</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.28505099159684</v>
+        <v>7.142214548395545</v>
       </c>
       <c r="C3" t="n">
-        <v>15.12382338392211</v>
+        <v>24.59768872990384</v>
       </c>
       <c r="D3" t="n">
-        <v>35.47054455443726</v>
+        <v>40.5363627083508</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.04871183678062</v>
+        <v>15.43012866764712</v>
       </c>
       <c r="C4" t="n">
-        <v>52.28886447588937</v>
+        <v>69.31433316293754</v>
       </c>
       <c r="D4" t="n">
-        <v>32.36625831360885</v>
+        <v>51.53586398673207</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.50656611985813</v>
+        <v>18.97227438456961</v>
       </c>
       <c r="C5" t="n">
-        <v>81.95138961200252</v>
+        <v>97.09484795000957</v>
       </c>
       <c r="D5" t="n">
-        <v>27.93072218582176</v>
+        <v>39.51534509593412</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.59876828859932</v>
+        <v>13.16229147083699</v>
       </c>
       <c r="C6" t="n">
-        <v>66.1334706011779</v>
+        <v>88.59389457893643</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>36.70951015719674</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>7.306166415004762</v>
       </c>
       <c r="C7" t="n">
-        <v>30.60205768907732</v>
+        <v>40.72289477215769</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>36.89015173477814</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.553926689373453</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.050377601959345</v>
+        <v>17.34465471240573</v>
       </c>
       <c r="C21" t="n">
-        <v>66.97858721861377</v>
+        <v>115.3419538374981</v>
       </c>
       <c r="D21" t="n">
-        <v>4.40648600122459</v>
+        <v>4.336163678101432</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.116869034534376</v>
+        <v>1.511891464540088</v>
       </c>
       <c r="C2" t="n">
-        <v>3.319288988058466</v>
+        <v>12.11083967958865</v>
       </c>
       <c r="D2" t="n">
-        <v>29.86280166777948</v>
+        <v>23.75731269506856</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.89159114637213</v>
+        <v>6.376451339083033</v>
       </c>
       <c r="C3" t="n">
-        <v>18.49612674800991</v>
+        <v>35.32328239880024</v>
       </c>
       <c r="D3" t="n">
-        <v>46.49557127312895</v>
+        <v>42.75020378142736</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.93232582833176</v>
+        <v>14.44739921569606</v>
       </c>
       <c r="C4" t="n">
-        <v>43.35496036724339</v>
+        <v>65.14092367218436</v>
       </c>
       <c r="D4" t="n">
-        <v>43.13799412460484</v>
+        <v>59.27007240078844</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.34858685493241</v>
+        <v>21.20575041173111</v>
       </c>
       <c r="C5" t="n">
-        <v>91.13073064671019</v>
+        <v>112.7782675253524</v>
       </c>
       <c r="D5" t="n">
-        <v>33.99301425954582</v>
+        <v>47.63930734857648</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.86294053649972</v>
+        <v>19.07928488433252</v>
       </c>
       <c r="C6" t="n">
-        <v>103.97002712285</v>
+        <v>120.0304378166235</v>
       </c>
       <c r="D6" t="n">
-        <v>33.16736444027425</v>
+        <v>40.77492740048278</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.83947640258903</v>
+        <v>11.37845589222053</v>
       </c>
       <c r="C7" t="n">
-        <v>68.45039518320036</v>
+        <v>83.54182089288233</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>38.92629647338602</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>39.30426933952106</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.91183229972957</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.85168364786328</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.270643927477344</v>
+        <v>17.74443357082434</v>
       </c>
       <c r="C21" t="n">
-        <v>76.34176123851211</v>
+        <v>128.6471433884765</v>
       </c>
       <c r="D21" t="n">
-        <v>5.452982945608007</v>
+        <v>5.323330071247302</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.197372346282614</v>
+        <v>1.4156801895239</v>
       </c>
       <c r="C2" t="n">
-        <v>3.879866927183394</v>
+        <v>7.459319056867265</v>
       </c>
       <c r="D2" t="n">
-        <v>26.04674834137213</v>
+        <v>18.59921025695582</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.10481032464293</v>
+        <v>9.130253649495335</v>
       </c>
       <c r="C3" t="n">
-        <v>15.15818455357075</v>
+        <v>53.46597997328129</v>
       </c>
       <c r="D3" t="n">
-        <v>59.59699438630262</v>
+        <v>49.4162706932632</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.088464771036</v>
+        <v>10.18465068385641</v>
       </c>
       <c r="C4" t="n">
-        <v>44.66952054322987</v>
+        <v>96.94562229896403</v>
       </c>
       <c r="D4" t="n">
-        <v>56.74305381005714</v>
+        <v>56.80686741083319</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.71798603363646</v>
+        <v>10.7255936688964</v>
       </c>
       <c r="C5" t="n">
-        <v>84.97026380256145</v>
+        <v>71.71666979522951</v>
       </c>
       <c r="D5" t="n">
-        <v>41.55247158224626</v>
+        <v>38.53359739168732</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.37491411649783</v>
+        <v>7.044039777970865</v>
       </c>
       <c r="C6" t="n">
-        <v>126.7927160034756</v>
+        <v>55.02401357992099</v>
       </c>
       <c r="D6" t="n">
-        <v>36.79001346894498</v>
+        <v>25.64030479181395</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>113.1856928226148</v>
+        <v>27.60772719112455</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>63.00365892003904</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>32.17187226816797</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>32.96708790860789</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.478157129136349</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.99880698506801</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.543387487994305</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
